--- a/resultado_Tutorial 2 barras.xlsx
+++ b/resultado_Tutorial 2 barras.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="109">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="331" uniqueCount="108">
   <si>
     <t>Ângulo</t>
   </si>
@@ -61,9 +61,6 @@
     <t>Modificado sem contingência</t>
   </si>
   <si>
-    <t>Modificado com contingência</t>
-  </si>
-  <si>
     <t>40.00</t>
   </si>
   <si>
@@ -85,75 +82,75 @@
     <t xml:space="preserve"> 7.25</t>
   </si>
   <si>
+    <t>48.93</t>
+  </si>
+  <si>
     <t xml:space="preserve"> 4.27</t>
   </si>
   <si>
-    <t>48.93</t>
+    <t>51.91</t>
   </si>
   <si>
     <t>-25.5</t>
   </si>
   <si>
-    <t>78.71</t>
+    <t>54.89</t>
   </si>
   <si>
     <t>-55.2</t>
   </si>
   <si>
-    <t>108.4</t>
+    <t>57.86</t>
   </si>
   <si>
     <t>-85.0</t>
   </si>
   <si>
-    <t>138.2</t>
-  </si>
-  <si>
-    <t>111.4</t>
+    <t>87.64</t>
   </si>
   <si>
     <t>-114.</t>
   </si>
   <si>
-    <t>114.4</t>
+    <t>117.4</t>
   </si>
   <si>
     <t>-144.</t>
   </si>
   <si>
-    <t>117.4</t>
+    <t>147.1</t>
+  </si>
+  <si>
+    <t>120.3</t>
   </si>
   <si>
     <t>-174.</t>
   </si>
   <si>
-    <t>120.3</t>
+    <t>123.3</t>
   </si>
   <si>
     <t>-147.</t>
   </si>
   <si>
-    <t>123.3</t>
+    <t>126.3</t>
   </si>
   <si>
     <t>-150.</t>
   </si>
   <si>
-    <t>126.3</t>
+    <t>129.3</t>
   </si>
   <si>
     <t>-153.</t>
   </si>
   <si>
-    <t>129.3</t>
+    <t>132.3</t>
   </si>
   <si>
     <t>-183.</t>
   </si>
   <si>
-    <t>132.3</t>
-  </si>
-  <si>
     <t>-213.</t>
   </si>
   <si>
@@ -220,67 +217,67 @@
     <t>-19.6</t>
   </si>
   <si>
+    <t>22.08</t>
+  </si>
+  <si>
     <t>-22.5</t>
   </si>
   <si>
-    <t>22.08</t>
+    <t>25.06</t>
   </si>
   <si>
     <t>-52.3</t>
   </si>
   <si>
-    <t>51.86</t>
+    <t>28.04</t>
   </si>
   <si>
     <t>-82.1</t>
   </si>
   <si>
-    <t>81.63</t>
+    <t>31.01</t>
   </si>
   <si>
     <t>-111.</t>
   </si>
   <si>
-    <t>84.61</t>
+    <t>60.79</t>
   </si>
   <si>
     <t>-141.</t>
   </si>
   <si>
-    <t>87.58</t>
+    <t>90.56</t>
   </si>
   <si>
     <t>-171.</t>
   </si>
   <si>
-    <t>90.56</t>
+    <t>93.54</t>
   </si>
   <si>
     <t>-201.</t>
   </si>
   <si>
-    <t>93.54</t>
-  </si>
-  <si>
     <t>96.52</t>
   </si>
   <si>
+    <t>99.49</t>
+  </si>
+  <si>
     <t>-177.</t>
   </si>
   <si>
-    <t>99.49</t>
+    <t>102.4</t>
   </si>
   <si>
     <t>-180.</t>
   </si>
   <si>
-    <t>102.4</t>
+    <t>105.4</t>
   </si>
   <si>
     <t>-210.</t>
-  </si>
-  <si>
-    <t>105.4</t>
   </si>
   <si>
     <t>-239.</t>
@@ -718,19 +715,19 @@
         <v>13</v>
       </c>
       <c r="D2" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="E2" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="F2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H2" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I2" t="b">
         <v>1</v>
@@ -747,25 +744,25 @@
         <v>14</v>
       </c>
       <c r="D3" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="E3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="F3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I3" t="b">
         <v>1</v>
       </c>
       <c r="J3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="4" spans="1:10">
@@ -776,22 +773,22 @@
         <v>2</v>
       </c>
       <c r="C4" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D4" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="E4" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="F4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H4" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I4" t="b">
         <v>1</v>
@@ -805,22 +802,22 @@
         <v>3</v>
       </c>
       <c r="C5" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D5" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="E5" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="F5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H5" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I5" t="b">
         <v>1</v>
@@ -837,25 +834,25 @@
         <v>14</v>
       </c>
       <c r="D6" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="E6" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="F6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H6" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I6" t="b">
         <v>1</v>
       </c>
       <c r="J6" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="7" spans="1:10">
@@ -866,22 +863,22 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D7" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="E7" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="F7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H7" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I7" t="b">
         <v>1</v>
@@ -895,22 +892,22 @@
         <v>4</v>
       </c>
       <c r="C8" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D8" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="E8" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="F8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="G8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H8" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I8" t="b">
         <v>1</v>
@@ -918,7 +915,7 @@
     </row>
     <row r="9" spans="1:10">
       <c r="A9" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B9">
         <v>5</v>
@@ -927,19 +924,19 @@
         <v>14</v>
       </c>
       <c r="D9" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="E9" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
       <c r="F9" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H9" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I9" t="b">
         <v>1</v>
@@ -947,28 +944,28 @@
     </row>
     <row r="10" spans="1:10">
       <c r="A10" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B10">
         <v>5</v>
       </c>
       <c r="C10" t="s">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="D10" t="s">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="E10" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="F10" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H10" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I10" t="b">
         <v>1</v>
@@ -976,7 +973,7 @@
     </row>
     <row r="11" spans="1:10">
       <c r="A11" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B11">
         <v>6</v>
@@ -985,19 +982,19 @@
         <v>14</v>
       </c>
       <c r="D11" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="E11" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F11" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H11" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I11" t="b">
         <v>1</v>
@@ -1005,7 +1002,7 @@
     </row>
     <row r="12" spans="1:10">
       <c r="A12" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B12">
         <v>6</v>
@@ -1014,19 +1011,19 @@
         <v>14</v>
       </c>
       <c r="D12" t="s">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="E12" t="s">
-        <v>71</v>
+        <v>70</v>
       </c>
       <c r="F12" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H12" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I12" t="b">
         <v>1</v>
@@ -1034,7 +1031,7 @@
     </row>
     <row r="13" spans="1:10">
       <c r="A13" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B13">
         <v>7</v>
@@ -1043,19 +1040,19 @@
         <v>14</v>
       </c>
       <c r="D13" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="E13" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
       <c r="F13" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="G13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H13" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I13" t="b">
         <v>1</v>
@@ -1063,7 +1060,7 @@
     </row>
     <row r="14" spans="1:10">
       <c r="A14" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B14">
         <v>7</v>
@@ -1072,19 +1069,19 @@
         <v>14</v>
       </c>
       <c r="D14" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="E14" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="F14" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H14" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I14" t="b">
         <v>1</v>
@@ -1092,7 +1089,7 @@
     </row>
     <row r="15" spans="1:10">
       <c r="A15" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B15">
         <v>8</v>
@@ -1101,19 +1098,19 @@
         <v>14</v>
       </c>
       <c r="D15" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="E15" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="F15" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H15" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I15" t="b">
         <v>1</v>
@@ -1121,34 +1118,31 @@
     </row>
     <row r="16" spans="1:10">
       <c r="A16" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B16">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="C16" t="s">
         <v>14</v>
       </c>
       <c r="D16" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="E16" t="s">
-        <v>31</v>
+        <v>74</v>
       </c>
       <c r="F16" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H16" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I16" t="b">
         <v>1</v>
-      </c>
-      <c r="J16" t="s">
-        <v>107</v>
       </c>
     </row>
     <row r="17" spans="1:10">
@@ -1156,25 +1150,25 @@
         <v>11</v>
       </c>
       <c r="B17">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="C17" t="s">
         <v>14</v>
       </c>
       <c r="D17" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="E17" t="s">
         <v>75</v>
       </c>
       <c r="F17" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H17" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I17" t="b">
         <v>1</v>
@@ -1191,19 +1185,19 @@
         <v>14</v>
       </c>
       <c r="D18" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="E18" t="s">
         <v>76</v>
       </c>
       <c r="F18" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H18" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I18" t="b">
         <v>1</v>
@@ -1214,25 +1208,25 @@
         <v>11</v>
       </c>
       <c r="B19">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="C19" t="s">
         <v>14</v>
       </c>
       <c r="D19" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="E19" t="s">
         <v>77</v>
       </c>
       <c r="F19" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H19" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I19" t="b">
         <v>1</v>
@@ -1249,19 +1243,19 @@
         <v>14</v>
       </c>
       <c r="D20" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="E20" t="s">
         <v>78</v>
       </c>
       <c r="F20" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H20" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I20" t="b">
         <v>1</v>
@@ -1278,27 +1272,30 @@
         <v>14</v>
       </c>
       <c r="D21" t="s">
+        <v>34</v>
+      </c>
+      <c r="E21" t="s">
         <v>35</v>
       </c>
-      <c r="E21" t="s">
-        <v>79</v>
-      </c>
       <c r="F21" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H21" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I21" t="b">
         <v>1</v>
+      </c>
+      <c r="J21" t="s">
+        <v>106</v>
       </c>
     </row>
     <row r="22" spans="1:10">
       <c r="A22" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B22">
         <v>11</v>
@@ -1307,30 +1304,27 @@
         <v>14</v>
       </c>
       <c r="D22" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="E22" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="F22" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H22" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I22" t="b">
         <v>1</v>
-      </c>
-      <c r="J22" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="23" spans="1:10">
       <c r="A23" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B23">
         <v>11</v>
@@ -1339,27 +1333,30 @@
         <v>14</v>
       </c>
       <c r="D23" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="E23" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
       <c r="F23" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H23" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I23" t="b">
         <v>1</v>
+      </c>
+      <c r="J23" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="24" spans="1:10">
       <c r="A24" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B24">
         <v>12</v>
@@ -1368,19 +1365,19 @@
         <v>14</v>
       </c>
       <c r="D24" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="E24" t="s">
-        <v>36</v>
+        <v>81</v>
       </c>
       <c r="F24" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H24" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I24" t="b">
         <v>1</v>
@@ -1388,7 +1385,7 @@
     </row>
     <row r="25" spans="1:10">
       <c r="A25" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B25">
         <v>12</v>
@@ -1397,19 +1394,19 @@
         <v>14</v>
       </c>
       <c r="D25" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="E25" t="s">
-        <v>82</v>
+        <v>36</v>
       </c>
       <c r="F25" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="H25" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I25" t="b">
         <v>1</v>
@@ -1417,7 +1414,7 @@
     </row>
     <row r="26" spans="1:10">
       <c r="A26" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B26">
         <v>13</v>
@@ -1426,27 +1423,30 @@
         <v>14</v>
       </c>
       <c r="D26" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="E26" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="F26" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G26" t="s">
         <v>104</v>
       </c>
       <c r="H26" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I26" t="b">
         <v>1</v>
+      </c>
+      <c r="J26" t="s">
+        <v>107</v>
       </c>
     </row>
     <row r="27" spans="1:10">
       <c r="A27" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B27">
         <v>13</v>
@@ -1455,30 +1455,27 @@
         <v>14</v>
       </c>
       <c r="D27" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="E27" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="F27" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G27" t="s">
-        <v>105</v>
+        <v>103</v>
       </c>
       <c r="H27" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I27" t="b">
         <v>1</v>
-      </c>
-      <c r="J27" t="s">
-        <v>108</v>
       </c>
     </row>
     <row r="28" spans="1:10">
       <c r="A28" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B28">
         <v>14</v>
@@ -1487,19 +1484,19 @@
         <v>14</v>
       </c>
       <c r="D28" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E28" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="F28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G28" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H28" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I28" t="b">
         <v>1</v>
@@ -1507,7 +1504,7 @@
     </row>
     <row r="29" spans="1:10">
       <c r="A29" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B29">
         <v>14</v>
@@ -1516,19 +1513,19 @@
         <v>14</v>
       </c>
       <c r="D29" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E29" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="F29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G29" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H29" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I29" t="b">
         <v>1</v>
@@ -1536,7 +1533,7 @@
     </row>
     <row r="30" spans="1:10">
       <c r="A30" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B30">
         <v>15</v>
@@ -1545,27 +1542,27 @@
         <v>14</v>
       </c>
       <c r="D30" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E30" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="F30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G30" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H30" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I30" t="b">
-        <v>1</v>
+        <v>0</v>
       </c>
     </row>
     <row r="31" spans="1:10">
       <c r="A31" t="s">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="B31">
         <v>15</v>
@@ -1574,22 +1571,22 @@
         <v>14</v>
       </c>
       <c r="D31" t="s">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E31" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="F31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G31" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H31" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I31" t="b">
-        <v>0</v>
+        <v>1</v>
       </c>
     </row>
     <row r="32" spans="1:10">
@@ -1603,19 +1600,19 @@
         <v>14</v>
       </c>
       <c r="D32" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E32" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="F32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G32" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H32" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I32" t="b">
         <v>1</v>
@@ -1632,19 +1629,19 @@
         <v>14</v>
       </c>
       <c r="D33" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="E33" t="s">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="F33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G33" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H33" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I33" t="b">
         <v>1</v>
@@ -1661,19 +1658,19 @@
         <v>14</v>
       </c>
       <c r="D34" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="E34" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="F34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G34" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H34" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I34" t="b">
         <v>1</v>
@@ -1690,19 +1687,19 @@
         <v>14</v>
       </c>
       <c r="D35" t="s">
-        <v>49</v>
+        <v>48</v>
       </c>
       <c r="E35" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="F35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G35" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H35" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I35" t="b">
         <v>1</v>
@@ -1719,19 +1716,19 @@
         <v>14</v>
       </c>
       <c r="D36" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
       <c r="E36" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="F36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G36" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H36" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I36" t="b">
         <v>1</v>
@@ -1748,25 +1745,25 @@
         <v>14</v>
       </c>
       <c r="D37" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="E37" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="F37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G37" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H37" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I37" t="b">
         <v>1</v>
       </c>
       <c r="J37" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
     </row>
     <row r="38" spans="1:10">
@@ -1780,19 +1777,19 @@
         <v>14</v>
       </c>
       <c r="D38" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="E38" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="F38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G38" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H38" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I38" t="b">
         <v>1</v>
@@ -1809,19 +1806,19 @@
         <v>14</v>
       </c>
       <c r="D39" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="E39" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="F39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G39" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H39" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I39" t="b">
         <v>1</v>
@@ -1838,19 +1835,19 @@
         <v>14</v>
       </c>
       <c r="D40" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
       <c r="E40" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="F40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G40" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H40" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I40" t="b">
         <v>1</v>
@@ -1867,19 +1864,19 @@
         <v>14</v>
       </c>
       <c r="D41" t="s">
-        <v>55</v>
+        <v>54</v>
       </c>
       <c r="E41" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="F41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G41" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H41" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I41" t="b">
         <v>1</v>
@@ -1896,19 +1893,19 @@
         <v>14</v>
       </c>
       <c r="D42" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="E42" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="F42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G42" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H42" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I42" t="b">
         <v>1</v>
@@ -1925,19 +1922,19 @@
         <v>14</v>
       </c>
       <c r="D43" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="E43" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="F43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G43" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H43" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I43" t="b">
         <v>1</v>
@@ -1954,19 +1951,19 @@
         <v>14</v>
       </c>
       <c r="D44" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
       <c r="E44" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="F44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G44" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H44" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I44" t="b">
         <v>1</v>
@@ -1983,19 +1980,19 @@
         <v>14</v>
       </c>
       <c r="D45" t="s">
-        <v>59</v>
+        <v>58</v>
       </c>
       <c r="E45" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="F45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G45" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H45" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I45" t="b">
         <v>1</v>
@@ -2012,19 +2009,19 @@
         <v>14</v>
       </c>
       <c r="D46" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
       <c r="E46" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
       <c r="F46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="G46" t="s">
-        <v>105</v>
+        <v>104</v>
       </c>
       <c r="H46" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
       <c r="I46" t="b">
         <v>0</v>
